--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0145.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0145.xlsx
@@ -17019,7 +17019,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Đợi ta nghĩ đã...</t>
+          <t>Đợi tao nghĩ đã...</t>
         </is>
       </c>
     </row>
@@ -18189,7 +18189,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>{PlayerName}, nếu có điều gì muốn nói mà không tìm được lời, cứ hát lên đi, biết đâu ta sẽ hiểu.</t>
+          <t>{PlayerName}, nếu có điều gì muốn nói mà không tìm được lời, cứ hát lên đi, biết đâu tao sẽ hiểu.</t>
         </is>
       </c>
     </row>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Ra là vậy...</t>
+          <t>Ta hiểu rồi...</t>
         </is>
       </c>
     </row>
@@ -19944,7 +19944,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Cứ gọi ta là Ciaccona thôi! Đừng có làm phức tạp hóa mọi chuyện.</t>
+          <t>Cứ gọi tao là Ciaccona thôi! Đừng có làm phức tạp hóa mọi chuyện.</t>
         </is>
       </c>
     </row>
@@ -20399,7 +20399,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Cô ấy cũng không có ở đây... Chào các {Male=anh chị;Female=chị em} nhé!</t>
+          <t>Cô ấy cũng không có ở đây... Chào các {Male=Brother and Sister;Female=Sisters} nhé!</t>
         </is>
       </c>
     </row>
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Bọn cậu tụ tập ở đây làm gì thế?</t>
+          <t>Bọn mày tụ tập ở đây làm gì thế?</t>
         </is>
       </c>
     </row>
@@ -20789,7 +20789,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Cảm ơn lời khen của {Male=ngài;Female=bà}. Đây là trang phục nghi lễ của chúng tôi. Chúng tôi đang tập những bài thánh ca để hát trong buổi lễ.</t>
+          <t>Cảm ơn lời khen của {Male=Sir;Female=Madam}. Đây là trang phục nghi lễ của chúng tôi. Chúng tôi đang tập những bài thánh ca để hát trong buổi lễ.</t>
         </is>
       </c>
     </row>
@@ -24039,7 +24039,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Ta lại lạc vào một giai điệu khác rồi.</t>
+          <t>Tao lại lạc vào một giai điệu khác rồi.</t>
         </is>
       </c>
     </row>
@@ -25274,7 +25274,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Bạn đang làm gì vậy?</t>
+          <t>Anh đang làm gì thế?</t>
         </is>
       </c>
     </row>
@@ -25339,7 +25339,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Tất nhiên là chơi một bản nhạc rồi. Ta muốn nắm bắt tâm trạng mà họ đã cảm nhận khi ở đây... Ta tò mò không biết họ đã để lại gì.</t>
+          <t>Tất nhiên là chơi một bản nhạc rồi. Tao muốn nắm bắt tâm trạng mà họ đã cảm nhận khi ở đây... Tao tò mò không biết họ đã để lại gì.</t>
         </is>
       </c>
     </row>
@@ -27354,7 +27354,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Haha, e là cậu hiểu nhầm rồi... Ta thừa nhận bị hỏi câu này suốt. Ta chỉ là một nhà viết kịch lang thang thôi.</t>
+          <t>Haha, e là cậu hiểu nhầm rồi... Tao thừa nhận bị hỏi câu này suốt. Tao chỉ là một nhà viết kịch lang thang thôi.</t>
         </is>
       </c>
     </row>
@@ -28459,7 +28459,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Ta nghĩ có thể nói tác giả của nó là dân quen thuộc trong những vòng bí mật đó. Thậm chí hắn có thể chính là Cộng Hưởng Giả mà chúng ta đang đồn đoán.</t>
+          <t>Tao nghĩ có thể nói tác giả của nó là dân quen thuộc trong những vòng bí mật đó. Thậm chí hắn có thể chính là Resonator mà chúng ta đang đồn đoán.</t>
         </is>
       </c>
     </row>
@@ -29564,7 +29564,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Vậy mà ta cứ tưởng cậu sẽ khôn ngoan hơn thế này nhiều.</t>
+          <t>Vậy mà tao cứ tưởng cậu sẽ khôn ngoan hơn thế này nhiều.</t>
         </is>
       </c>
     </row>
@@ -31904,7 +31904,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Đây... là một bài thơ ta chưa từng thấy. Nó khác hẳn những gì người ta vẫn viết trước đây.</t>
+          <t>Đây... là một bài thơ tao chưa từng thấy. Nó khác hẳn những gì người ta vẫn viết trước đây.</t>
         </is>
       </c>
     </row>
